--- a/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 12,51</t>
+          <t>-11,32; 12,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 8,33</t>
+          <t>-12,43; 8,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -0,7</t>
+          <t>-23,9; -0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 8,18</t>
+          <t>-7,52; 8,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 141,99</t>
+          <t>-53,55; 137,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 150,42</t>
+          <t>-69,84; 168,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,2; 13,95</t>
+          <t>-88,47; 5,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 181,97</t>
+          <t>-59,7; 155,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 3,63</t>
+          <t>-22,38; 6,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 19,58</t>
+          <t>-5,48; 19,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 18,0</t>
+          <t>-6,13; 17,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 8,22</t>
+          <t>-12,41; 8,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,71; 38,63</t>
+          <t>-78,06; 66,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 209,79</t>
+          <t>-28,48; 208,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 231,49</t>
+          <t>-36,27; 235,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 94,07</t>
+          <t>-59,45; 99,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 19,02</t>
+          <t>-9,07; 17,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 12,01</t>
+          <t>-16,72; 14,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 4,93</t>
+          <t>-17,39; 6,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 28,12</t>
+          <t>-1,49; 28,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 166,59</t>
+          <t>-42,07; 154,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,72; 71,06</t>
+          <t>-53,35; 90,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,95</t>
+          <t>-100,0; 194,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 765,11</t>
+          <t>-29,87; 590,19</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 10,04</t>
+          <t>-6,84; 11,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 14,35</t>
+          <t>-5,24; 13,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 6,91</t>
+          <t>-10,05; 7,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 4,44</t>
+          <t>-14,94; 5,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 72,14</t>
+          <t>-32,0; 85,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 89,08</t>
+          <t>-21,81; 92,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 54,44</t>
+          <t>-43,77; 51,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 24,18</t>
+          <t>-46,27; 27,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 21,38</t>
+          <t>-3,03; 21,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 8,86</t>
+          <t>-14,05; 9,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 15,19</t>
+          <t>-7,01; 16,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 21,39</t>
+          <t>-2,26; 24,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 154,5</t>
+          <t>-15,07; 140,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 45,25</t>
+          <t>-42,54; 52,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 99,0</t>
+          <t>-27,74; 105,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 222,23</t>
+          <t>-17,16; 239,21</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 33,33</t>
+          <t>6,41; 33,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 13,5</t>
+          <t>-16,89; 13,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 18,1</t>
+          <t>-16,48; 18,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 16,14</t>
+          <t>-7,59; 17,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,02; 1372,42</t>
+          <t>30,56; 1132,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 115,97</t>
+          <t>-70,42; 133,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 140,24</t>
+          <t>-55,4; 141,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 531,18</t>
+          <t>-53,46; 588,42</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 8,18</t>
+          <t>-1,41; 8,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,33</t>
+          <t>-4,64; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,27</t>
+          <t>-5,95; 3,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,36</t>
+          <t>-2,78; 6,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 56,27</t>
+          <t>-7,27; 54,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 36,83</t>
+          <t>-21,64; 31,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 25,53</t>
+          <t>-28,52; 21,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 45,0</t>
+          <t>-15,85; 49,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 12,58</t>
+          <t>-9,95; 11,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 8,71</t>
+          <t>-12,59; 8,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,9; -0,74</t>
+          <t>-24,27; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 8,27</t>
+          <t>-7,27; 8,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 137,25</t>
+          <t>-49,57; 137,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,84; 168,7</t>
+          <t>-72,73; 159,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-88,47; 5,34</t>
+          <t>-86,14; 13,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 155,1</t>
+          <t>-59,79; 167,11</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 6,26</t>
+          <t>-21,26; 5,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 19,9</t>
+          <t>-5,98; 19,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 17,23</t>
+          <t>-5,21; 18,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 8,22</t>
+          <t>-12,41; 8,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,06; 66,43</t>
+          <t>-78,17; 52,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 208,27</t>
+          <t>-30,35; 210,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 235,01</t>
+          <t>-30,37; 254,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 99,46</t>
+          <t>-61,31; 83,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 17,4</t>
+          <t>-9,0; 19,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 14,46</t>
+          <t>-18,19; 13,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 6,07</t>
+          <t>-17,83; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 28,78</t>
+          <t>-2,26; 30,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 154,19</t>
+          <t>-42,49; 161,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 90,48</t>
+          <t>-57,04; 84,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 194,79</t>
+          <t>-93,3; 180,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 590,19</t>
+          <t>-26,43; 612,92</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 11,04</t>
+          <t>-7,81; 9,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,79</t>
+          <t>-5,39; 13,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 7,26</t>
+          <t>-10,72; 7,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 5,79</t>
+          <t>-16,49; 4,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 85,33</t>
+          <t>-35,95; 73,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 92,77</t>
+          <t>-21,76; 90,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 51,6</t>
+          <t>-47,45; 45,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 27,56</t>
+          <t>-49,81; 22,24</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 21,95</t>
+          <t>-3,13; 21,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 9,08</t>
+          <t>-14,71; 8,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 16,12</t>
+          <t>-9,06; 14,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 24,36</t>
+          <t>-2,85; 23,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 140,45</t>
+          <t>-13,38; 140,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 52,06</t>
+          <t>-44,98; 47,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 105,94</t>
+          <t>-33,35; 89,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 239,21</t>
+          <t>-22,21; 226,78</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 33,3</t>
+          <t>6,27; 32,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 13,21</t>
+          <t>-16,66; 12,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 18,69</t>
+          <t>-17,2; 16,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 17,58</t>
+          <t>-6,18; 17,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,56; 1132,09</t>
+          <t>35,62; 1372,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,42; 133,22</t>
+          <t>-73,81; 119,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 141,07</t>
+          <t>-56,82; 132,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 588,42</t>
+          <t>-54,54; 586,66</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,07</t>
+          <t>-1,21; 8,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,58</t>
+          <t>-4,1; 5,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,51</t>
+          <t>-5,54; 4,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,65</t>
+          <t>-3,02; 6,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 54,1</t>
+          <t>-7,13; 58,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 31,22</t>
+          <t>-18,89; 29,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 21,37</t>
+          <t>-26,67; 26,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 49,02</t>
+          <t>-16,93; 44,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 11,6</t>
+          <t>-9,99; 12,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 8,9</t>
+          <t>-13,51; 8,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 0,55</t>
+          <t>-23,13; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 8,03</t>
+          <t>-6,61; 8,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 137,38</t>
+          <t>-49,36; 141,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 159,51</t>
+          <t>-75,6; 150,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,14; 13,8</t>
+          <t>-86,2; 13,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 167,11</t>
+          <t>-60,12; 205,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,72%</t>
+          <t>-10,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 5,38</t>
+          <t>-22,99; 3,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 19,0</t>
+          <t>-5,97; 19,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 18,01</t>
+          <t>-5,79; 18,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 8,09</t>
+          <t>-12,11; 8,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 52,78</t>
+          <t>-80,71; 38,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 210,3</t>
+          <t>-32,77; 209,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 254,68</t>
+          <t>-33,19; 231,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 83,13</t>
+          <t>-61,12; 104,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>122,4%</t>
+          <t>111,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 19,05</t>
+          <t>-10,96; 19,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 13,67</t>
+          <t>-18,55; 12,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 4,95</t>
+          <t>-17,85; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 30,3</t>
+          <t>-2,17; 26,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 161,91</t>
+          <t>-49,78; 166,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 84,6</t>
+          <t>-58,72; 71,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-93,3; 180,1</t>
+          <t>-100,0; 141,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 612,92</t>
+          <t>-19,81; 816,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,18%</t>
+          <t>-11,97%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 9,62</t>
+          <t>-6,59; 10,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 13,93</t>
+          <t>-5,21; 14,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 7,02</t>
+          <t>-10,39; 6,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 4,47</t>
+          <t>-13,26; 6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 73,96</t>
+          <t>-31,64; 72,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 90,32</t>
+          <t>-22,64; 89,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 45,89</t>
+          <t>-44,89; 54,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 22,24</t>
+          <t>-42,99; 36,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 21,03</t>
+          <t>-4,11; 21,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 8,55</t>
+          <t>-14,35; 8,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 14,11</t>
+          <t>-8,05; 15,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 23,86</t>
+          <t>-5,38; 16,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 140,52</t>
+          <t>-14,97; 154,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 47,26</t>
+          <t>-43,84; 45,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 89,73</t>
+          <t>-29,35; 99,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 226,78</t>
+          <t>-29,45; 168,79</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 32,19</t>
+          <t>7,21; 33,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 12,92</t>
+          <t>-17,02; 13,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 16,71</t>
+          <t>-16,13; 18,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 17,28</t>
+          <t>-7,71; 16,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,62; 1372,66</t>
+          <t>18,02; 1372,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,81; 119,2</t>
+          <t>-72,26; 115,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 132,85</t>
+          <t>-53,69; 140,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 586,66</t>
+          <t>-54,69; 493,93</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 8,42</t>
+          <t>-1,17; 8,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,41</t>
+          <t>-4,06; 6,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,0</t>
+          <t>-5,36; 4,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,27</t>
+          <t>-3,05; 5,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 58,54</t>
+          <t>-7,53; 56,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 29,81</t>
+          <t>-17,71; 36,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 26,93</t>
+          <t>-26,42; 25,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 44,48</t>
+          <t>-17,83; 43,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-12,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-14,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-59,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7932891441570278</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.700201345604675</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-12.31042759547142</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.3582287524496408</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.05238660313863158</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1465089571776454</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.5919096706046401</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.04113768784859444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,99; 12,51</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 8,33</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-23,13; -0,7</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,61; 8,44</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-49,36; 141,99</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-75,6; 150,42</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-86,2; 13,95</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-60,12; 205,8</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.993473150450844</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-13.5107914092917</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-23.13440969456938</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.605971519787089</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4936234067855037</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7560351994098164</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8620269518750984</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6011833641797852</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.51245654705638</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.334257636420867</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.702067485960703</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.437037457014904</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.419879175547948</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.504211516847084</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1394960443511169</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.057954406462802</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-8,46</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-42,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-10,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-22,99; 3,63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 19,58</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,79; 18,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,11; 8,74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-80,71; 38,63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-32,77; 209,79</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-33,19; 231,49</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-61,12; 104,37</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-8.459782433909435</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.793640820507973</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.865402902670086</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.59029094946028</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4218906291716688</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4486161370260838</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.4384067732526692</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1081389229242787</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-9,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-47,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>111,98%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-22.98696011415825</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.968571887709064</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.791009213326823</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-12.10528244264489</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8070945127764635</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.327715966891831</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3319039970168918</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6111944411909839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,96; 19,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-18,55; 12,01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-17,85; 4,93</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,17; 26,52</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-49,78; 166,59</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,72; 71,06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 141,95</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-19,81; 816,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.634433396559477</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>19.58175607401772</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17.99892610687267</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.738504896483745</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3862575115150009</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.097852145000551</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.314923920308163</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.04366661320566</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,43</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-9,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-11,97%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.239267867333095</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.237687764040328</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.787508094942958</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>11.17159510405706</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1880263699326885</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.09161174878216415</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4791683030291423</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.119834598897381</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 10,04</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 14,35</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,39; 6,91</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,26; 6,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-31,64; 72,14</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-22,64; 89,08</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-44,89; 54,44</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-42,99; 36,67</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.96488507018656</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-18.54891611509372</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-17.84812050060404</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.173884385595367</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.497779046600988</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.587219830500972</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1981316758300407</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19.0155093243235</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.00564936830945</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.931438766520952</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>26.52244267893839</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.665869023686309</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7105907918538741</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.419501663158723</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>8.163734830013569</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>44,71%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-10,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 21,38</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-14,35; 8,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,05; 15,19</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,38; 16,28</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-14,97; 154,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-43,84; 45,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-29,35; 99,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-29,45; 168,79</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>1.187921213381193</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.432334376239544</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.824712249933072</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.044567222322272</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.06692603615234186</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2207922538278146</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.09721509233142789</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1196806303205618</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>19,31</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2,88</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>262,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-15,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62,83%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.589574479646906</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.209212996610915</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-10.38890515006413</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.26334465342836</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3163744001240106</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2264212290010418</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4488718877315468</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4298705146028222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>7,21; 33,33</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-17,02; 13,5</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-16,13; 18,1</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,71; 16,09</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>18,02; 1372,42</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-72,26; 115,97</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-53,69; 140,24</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-54,69; 493,93</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.03743516440214</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>14.34956422279256</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.914991841127143</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.925768086586487</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7214420206311039</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8907913276107148</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5444133683448721</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3667173041346918</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-5,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>9.192609635804036</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.833073803046138</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.592236419732836</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.341286157735064</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.4471238997814783</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1069801954688503</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.1653750948232458</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3691437286305269</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,17; 8,18</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 6,33</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 4,27</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,05; 5,72</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-7,53; 56,27</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-17,71; 36,83</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-26,42; 25,53</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-17,83; 43,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.106278282127438</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-14.34779117192355</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-8.054560500009794</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.375308144421478</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.14967014941397</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4383673318213494</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2934926233268401</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2945336159120957</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>21.37637631658613</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.864520728927811</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>15.18752396865899</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>16.2761632754935</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.544966264652278</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4525096256106129</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.9900101969917739</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.687885023465541</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>19.30507649094377</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-2.878728363189981</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.8852017106695947</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5.573559665569451</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2.627395358146885</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.158389536584637</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.03886279678998012</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.6282628362635715</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>7.207857045462767</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-17.01839514989486</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-16.13456990471728</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.711767563129712</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.1802421006602761</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.7225614450164575</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.5368740226587331</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.5469066248919251</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>33.32985412865789</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>13.50319794021284</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>18.10066276430047</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>16.08654653837849</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>13.72424282057046</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.159698029555139</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1.402437983738654</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>4.939287286756162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3.428759798876624</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.871075877755334</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.9456904650850279</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.471687588406412</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2013421704145543</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.04360746607125694</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.0509440105578256</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.09538786209650775</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.16651847827133</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.063996474237086</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.358787363858681</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.053852778352323</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.07533554643619569</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1771328013029342</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2641827238956323</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.178328857956234</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8.181368112232851</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>6.328043787590497</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.270529490945004</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.724635593136107</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.5626551568173427</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.3683076541868319</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2553480519304276</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.4324524345210142</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
